--- a/ServeWay_Project/Assets/07.Data/IngredientDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/IngredientDataSet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371544FB-48A1-439B-99B8-806D6B669C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B642767-7643-470B-B2C3-3BA4806B9BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="22290" windowHeight="14685" xr2:uid="{EAC46937-06B9-4F5A-AE58-D1BFB26159AE}"/>
+    <workbookView xWindow="6870" yWindow="345" windowWidth="16125" windowHeight="14685" xr2:uid="{EAC46937-06B9-4F5A-AE58-D1BFB26159AE}"/>
   </bookViews>
   <sheets>
     <sheet name="IngredientList" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="97">
   <si>
     <t>_Index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -243,13 +243,6 @@
   </si>
   <si>
     <t>Ginger</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/Item/Item_1.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/Item/Item_1.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -434,6 +427,10 @@
   <si>
     <t>포만감 15% 감소
 손님의 공격 속도 10% 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -844,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -864,10 +861,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -884,10 +881,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -904,10 +901,10 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -924,10 +921,10 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -944,10 +941,10 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -964,10 +961,10 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -984,10 +981,10 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1004,10 +1001,10 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1024,10 +1021,10 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1044,10 +1041,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1064,10 +1061,10 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1084,10 +1081,10 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1104,10 +1101,10 @@
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1124,10 +1121,10 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1144,10 +1141,10 @@
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1164,10 +1161,10 @@
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1184,10 +1181,10 @@
         <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1204,10 +1201,10 @@
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1224,10 +1221,10 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1244,10 +1241,10 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1264,10 +1261,10 @@
         <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1284,10 +1281,10 @@
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1304,10 +1301,10 @@
         <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1324,10 +1321,10 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1344,10 +1341,10 @@
         <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1364,10 +1361,10 @@
         <v>26</v>
       </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1384,10 +1381,10 @@
         <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1404,10 +1401,10 @@
         <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1424,10 +1421,10 @@
         <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1444,10 +1441,10 @@
         <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1464,10 +1461,10 @@
         <v>31</v>
       </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1484,10 +1481,10 @@
         <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F34" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1504,10 +1501,10 @@
         <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1524,10 +1521,10 @@
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1544,10 +1541,10 @@
         <v>35</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1564,10 +1561,10 @@
         <v>36</v>
       </c>
       <c r="E38" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F38" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1584,10 +1581,10 @@
         <v>37</v>
       </c>
       <c r="E39" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1604,10 +1601,10 @@
         <v>38</v>
       </c>
       <c r="E40" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1624,10 +1621,10 @@
         <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1644,10 +1641,10 @@
         <v>40</v>
       </c>
       <c r="E42" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1664,10 +1661,10 @@
         <v>41</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="F43" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1675,7 +1672,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
@@ -1684,10 +1681,10 @@
         <v>42</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1695,7 +1692,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -1704,10 +1701,10 @@
         <v>43</v>
       </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
